--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,59 +1029,59 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>456.51</v>
+        <v>377.12</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>64.93000000000001</v>
+        <v>456.51</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>255.47</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>449.86</v>
+        <v>255.47</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,32 +2733,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2768,42 +2768,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>359.64</v>
+        <v>449.86</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,27 +2906,27 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
+          <t>344.0561698076144</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>510.95</v>
+        <v>359.64</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.88</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4967.0</t>
+          <t>3348.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4262.0</t>
+          <t>4081.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2968.4</t>
+          <t>3197.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1384.28</t>
+          <t>1444.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>884</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>310.3628294939249</t>
+          <t>341.2223925193826</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>593.89</v>
+        <v>510.95</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,79 +4026,79 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>46.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-112.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3917.0</t>
+          <t>4967.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3539.4</t>
+          <t>4262.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2765.5</t>
+          <t>2968.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1287.82</t>
+          <t>1384.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>258.8121005839618</t>
+          <t>310.3628294939249</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>517.71</v>
+        <v>593.89</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.25</t>
+          <t>-38.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>43.89</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.99</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5219.0</t>
+          <t>3917.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2971.8</t>
+          <t>3539.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2622.7</t>
+          <t>2765.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1222.4</t>
+          <t>1287.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>773</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>211.7405759301469</t>
+          <t>258.8121005839618</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>502.88</v>
+        <v>517.71</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-39.73</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>43.95</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-112.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2956.0</t>
+          <t>5219.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2549.4</t>
+          <t>2971.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2164.7</t>
+          <t>2622.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1120.14</t>
+          <t>1222.4</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>349</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>158.8064336699963</t>
+          <t>211.7405759301469</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>324.24</v>
+        <v>502.88</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-38.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,72 +5319,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.75</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7708.5</t>
+          <t>7705.024709302325</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4251.0</t>
+          <t>2956.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2313.0</t>
+          <t>2549.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1926.9</t>
+          <t>2164.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1071.52</t>
+          <t>1120.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>128.7281841879982</t>
+          <t>158.8064336699963</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>299.92</v>
+        <v>324.24</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-39.52</t>
+          <t>-39.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-10.78039812349436</t>
+          <t>-7.735853911671112</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-38.81131296150028</t>
+          <t>-4.485033608893704</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-11.0861416693264</t>
+          <t>-10.68337399707084</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>4044016.81</v>
+        <v>1370572.98</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,22 +5923,22 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>7481492.25</v>
+        <v>4044016.81</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,37 +6354,37 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>10514780.48</v>
+        <v>7481492.25</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,37 +6785,37 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>14618542.22</v>
+        <v>10514780.48</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,37 +7216,37 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
+          <t>2543942.421289739</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>16243824.98</v>
+        <v>14618542.22</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
+          <t>348560.6398269488</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-1710514.65</v>
+        <v>16243824.98</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,37 +8078,37 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>546.012</t>
+          <t>523.722</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -8336,42 +8336,42 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -8381,32 +8381,32 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.43</t>
+          <t>-114.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14095689.0</t>
+          <t>13427032.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12822875.6</t>
+          <t>13469101.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13707477.2</t>
+          <t>13623522.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>38208147.56</t>
+          <t>37794170.94</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-884601</t>
+          <t>-154420</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2692573.381566256</t>
+          <t>-2541487.422143453</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-1866957.84</v>
+        <v>-1710514.65</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,22 +8509,22 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>559.794</t>
+          <t>546.012</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.93</t>
+          <t>-115.43</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14163483.0</t>
+          <t>14095689.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>12156684.4</t>
+          <t>12822875.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>15987215.5</t>
+          <t>13707477.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>39179007.58</t>
+          <t>38208147.56</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3830531</t>
+          <t>-884601</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2842685.298585612</t>
+          <t>-2692573.381566256</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-2095412.87</v>
+        <v>-1866957.84</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>583.207</t>
+          <t>559.794</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.79</t>
+          <t>-23.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,132 +9218,132 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-4.04</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>25.53</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>25.82</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>27.81</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>7.55</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-115.93</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>158759446.9010116</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>14163483.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12156684.4</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>15987215.5</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>39179007.58</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-3830531</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-2842685.298585612</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-2095412.87</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
           <t>-0.59</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-4.09</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>26.97</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>8.46</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-116.23</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>158953592.6613603</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>14904039.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>11250126.4</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>17251100.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>40179740.36</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-6000973</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-2978553.01306491</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-2354204.67</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
           <t>三商電</t>
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>421.038</t>
+          <t>583.207</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>-34.79</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,247 +9644,247 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>25.87</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>26.97</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>8.46</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-116.23</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>158759446.9010116</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>14904039.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11250126.4</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>17251100.4</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>40179740.36</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-6000973</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-2978553.01306491</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-2354204.67</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>298.8215518698245</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>224.5227559584907</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>40.88738708368201</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>17.17</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>38.02%</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>三商電-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
           <t>25.65</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-116.57</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>158953592.6613603</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>10755264.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>11781293.6</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>17172812.5</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>41709522.14</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-5391518</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-3092070.894003837</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-2719173.79</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>-19.14649237353606</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>0.3555578184533659</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>29.10335467500664</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>17.37</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>38.02%</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>4.37%</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>5209</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>三商電-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
           <t>25.65</t>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>396.333</t>
+          <t>421.038</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.30</t>
+          <t>-31.40</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>624</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,52 +10075,52 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-116.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>158953592.6613603</t>
+          <t>158759446.9010116</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>10195903.0</t>
+          <t>10755264.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>13777942.6</t>
+          <t>11781293.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>17733098.4</t>
+          <t>17172812.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>42807181.94</t>
+          <t>41709522.14</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3955155</t>
+          <t>-5391518</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3159870.368294305</t>
+          <t>-3092070.894003837</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2698933.28</v>
+        <v>-2719173.79</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-19.14649237353606</t>
+          <t>298.8215518698245</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>0.3555578184533659</t>
+          <t>224.5227559584907</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>29.10335467500664</t>
+          <t>40.88738708368201</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>377.12</v>
+        <v>502.85</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,59 +1460,59 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>456.51</v>
+        <v>377.12</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>64.93000000000001</v>
+        <v>456.51</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>255.47</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>449.86</v>
+        <v>255.47</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,27 +3169,27 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,42 +3199,42 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>359.64</v>
+        <v>449.86</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
+          <t>344.0561698076144</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>510.95</v>
+        <v>359.64</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.88</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4967.0</t>
+          <t>3348.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4262.0</t>
+          <t>4081.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2968.4</t>
+          <t>3197.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1384.28</t>
+          <t>1444.32</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>884</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>310.3628294939249</t>
+          <t>341.2223925193826</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>593.89</v>
+        <v>510.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,74 +4462,74 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>46.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-112.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3917.0</t>
+          <t>4967.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3539.4</t>
+          <t>4262.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2765.5</t>
+          <t>2968.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1287.82</t>
+          <t>1384.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>258.8121005839618</t>
+          <t>310.3628294939249</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>517.71</v>
+        <v>593.89</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.25</t>
+          <t>-38.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,32 +4893,32 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,32 +4928,32 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>43.89</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.99</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5219.0</t>
+          <t>3917.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2971.8</t>
+          <t>3539.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2622.7</t>
+          <t>2765.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1222.4</t>
+          <t>1287.82</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>773</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>211.7405759301469</t>
+          <t>258.8121005839618</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>502.88</v>
+        <v>517.71</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-39.73</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>43.95</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-112.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7705.024709302325</t>
+          <t>7707.095791001451</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2956.0</t>
+          <t>5219.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2549.4</t>
+          <t>2971.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2164.7</t>
+          <t>2622.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1120.14</t>
+          <t>1222.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>349</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>158.8064336699963</t>
+          <t>211.7405759301469</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>324.24</v>
+        <v>502.88</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1370572.98</v>
+        <v>-457226.67</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>4044016.81</v>
+        <v>1370572.98</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>7481492.25</v>
+        <v>4044016.81</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>10514780.48</v>
+        <v>7481492.25</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>14618542.22</v>
+        <v>10514780.48</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
+          <t>2543942.421289739</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>16243824.98</v>
+        <v>14618542.22</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
+          <t>348560.6398269488</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-1710514.65</v>
+        <v>16243824.98</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>546.012</t>
+          <t>523.722</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -8767,42 +8767,42 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -8812,32 +8812,32 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.43</t>
+          <t>-114.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14095689.0</t>
+          <t>13427032.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>12822875.6</t>
+          <t>13469101.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13707477.2</t>
+          <t>13623522.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>38208147.56</t>
+          <t>37794170.94</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-884601</t>
+          <t>-154420</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2692573.381566256</t>
+          <t>-2541487.422143453</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-1866957.84</v>
+        <v>-1710514.65</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>559.794</t>
+          <t>546.012</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.93</t>
+          <t>-115.43</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158759446.9010116</t>
+          <t>158568108.9307359</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14163483.0</t>
+          <t>14095689.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>12156684.4</t>
+          <t>12822875.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15987215.5</t>
+          <t>13707477.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>39179007.58</t>
+          <t>38208147.56</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3830531</t>
+          <t>-884601</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2842685.298585612</t>
+          <t>-2692573.381566256</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-2095412.87</v>
+        <v>-1866957.84</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>583.207</t>
+          <t>559.794</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.79</t>
+          <t>-23.96</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,132 +9649,132 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-4.04</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>25.53</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>25.82</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>27.81</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>7.55</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-115.93</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>158568108.9307359</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>14163483.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12156684.4</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>15987215.5</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>39179007.58</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-3830531</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-2842685.298585612</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-2095412.87</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
           <t>-0.59</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-4.09</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>26.97</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>8.46</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-116.23</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>158759446.9010116</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>14904039.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>11250126.4</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>17251100.4</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>40179740.36</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-6000973</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-2978553.01306491</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-2354204.67</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
           <t>三商電</t>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>421.038</t>
+          <t>583.207</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-31.40</t>
+          <t>-34.79</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,247 +10075,247 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>25.87</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>26.97</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>8.46</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-116.23</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>158568108.9307359</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>14904039.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11250126.4</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>17251100.4</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>40179740.36</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-6000973</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-2978553.01306491</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-2354204.67</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>298.8215518698245</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>224.5227559584907</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>40.88738708368201</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>17.17</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>38.02%</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>27.86</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>三商電-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
           <t>25.65</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-116.57</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>158759446.9010116</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>10755264.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>11781293.6</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>17172812.5</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>41709522.14</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-5391518</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-3092070.894003837</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-2719173.79</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>298.8215518698245</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>224.5227559584907</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>40.88738708368201</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>38.02%</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>4.37%</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>28.27</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>5150</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>三商電-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
           <t>25.65</t>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>502.85</v>
+        <v>428.66</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>377.12</v>
+        <v>502.85</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,59 +1891,59 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>456.51</v>
+        <v>377.12</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>64.93000000000001</v>
+        <v>456.51</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>255.47</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>449.86</v>
+        <v>255.47</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,32 +3595,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3630,42 +3630,42 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>359.64</v>
+        <v>449.86</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
+          <t>344.0561698076144</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>510.95</v>
+        <v>359.64</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,72 +4457,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.88</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4967.0</t>
+          <t>3348.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4262.0</t>
+          <t>4081.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2968.4</t>
+          <t>3197.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1384.28</t>
+          <t>1444.32</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>884</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>310.3628294939249</t>
+          <t>341.2223925193826</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>593.89</v>
+        <v>510.95</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,79 +4888,79 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>46.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-112.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3917.0</t>
+          <t>4967.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3539.4</t>
+          <t>4262.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2765.5</t>
+          <t>2968.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1287.82</t>
+          <t>1384.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>258.8121005839618</t>
+          <t>310.3628294939249</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>517.71</v>
+        <v>593.89</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.25</t>
+          <t>-38.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,32 +5359,32 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>43.89</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.99</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7707.095791001451</t>
+          <t>7704.823913043478</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5219.0</t>
+          <t>3917.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2971.8</t>
+          <t>3539.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2622.7</t>
+          <t>2765.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1222.4</t>
+          <t>1287.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>773</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>211.7405759301469</t>
+          <t>258.8121005839618</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>502.88</v>
+        <v>517.71</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-39.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>43.95</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,42 +5619,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>537.759</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>26.35</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>669.773</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-457226.67</v>
+        <v>-1976159.79</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>1370572.98</v>
+        <v>-457226.67</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>4044016.81</v>
+        <v>1370572.98</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>7481492.25</v>
+        <v>4044016.81</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>10514780.48</v>
+        <v>7481492.25</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>14618542.22</v>
+        <v>10514780.48</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,240 +8336,240 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
+          <t>27.67</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>54.01</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-111.86</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>158370091.70317</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>66958254.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>71886475.4</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>41568300.9</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>42670245.7</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>30318174</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>2543942.421289739</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>14618542.22</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>298.8215518698245</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>224.5227559584907</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>40.88738708368201</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>17.34</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>38.02%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>42.50</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-113.46</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>158568108.9307359</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>250787919.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>61475632.4</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>36628463.0</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>41978510.2</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>24847169</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>348560.6398269488</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>16243824.98</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>298.8215518698245</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>224.5227559584907</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>40.88738708368201</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>38.02%</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>4.37%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
+          <t>348560.6398269488</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-1710514.65</v>
+        <v>16243824.98</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>546.012</t>
+          <t>523.722</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -9198,42 +9198,42 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.43</t>
+          <t>-114.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14095689.0</t>
+          <t>13427032.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>12822875.6</t>
+          <t>13469101.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13707477.2</t>
+          <t>13623522.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>38208147.56</t>
+          <t>37794170.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-884601</t>
+          <t>-154420</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2692573.381566256</t>
+          <t>-2541487.422143453</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1866957.84</v>
+        <v>-1710514.65</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>559.794</t>
+          <t>546.012</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.93</t>
+          <t>-115.43</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>158568108.9307359</t>
+          <t>158370091.70317</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14163483.0</t>
+          <t>14095689.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12156684.4</t>
+          <t>12822875.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>15987215.5</t>
+          <t>13707477.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>39179007.58</t>
+          <t>38208147.56</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3830531</t>
+          <t>-884601</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2842685.298585612</t>
+          <t>-2692573.381566256</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2095412.87</v>
+        <v>-1866957.84</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>583.207</t>
+          <t>559.794</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-34.79</t>
+          <t>-23.96</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>538</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,132 +10080,132 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-4.04</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>25.53</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>25.82</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>27.81</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>7.55</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-115.93</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>158370091.70317</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>14163483.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>12156684.4</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>15987215.5</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>39179007.58</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-3830531</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-2842685.298585612</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-2095412.87</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
           <t>-0.59</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-4.09</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>26.97</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>8.46</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-116.23</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>158568108.9307359</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>14904039.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>11250126.4</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>17251100.4</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>40179740.36</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-6000973</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-2978553.01306491</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-2354204.67</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
           <t>三商電</t>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4583.4</t>
+          <t>4580.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1978.44</t>
+          <t>1994.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>428.66</v>
+        <v>139.36</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>502.85</v>
+        <v>428.66</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>377.12</v>
+        <v>502.85</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,59 +2322,59 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>456.51</v>
+        <v>377.12</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>-5.71</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-22.63</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>64.93000000000001</v>
+        <v>456.51</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>255.47</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>449.86</v>
+        <v>255.47</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,32 +4026,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4061,42 +4061,42 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>359.64</v>
+        <v>449.86</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
+          <t>344.0561698076144</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>510.95</v>
+        <v>359.64</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,72 +4888,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.88</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4967.0</t>
+          <t>3348.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4262.0</t>
+          <t>4081.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2968.4</t>
+          <t>3197.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1384.28</t>
+          <t>1444.32</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>884</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>310.3628294939249</t>
+          <t>341.2223925193826</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>593.89</v>
+        <v>510.95</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.97</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,79 +5319,79 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>46.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-112.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7704.823913043478</t>
+          <t>7695.998552821997</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3917.0</t>
+          <t>4967.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3539.4</t>
+          <t>4262.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2765.5</t>
+          <t>2968.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1287.82</t>
+          <t>1384.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>258.8121005839618</t>
+          <t>310.3628294939249</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>517.71</v>
+        <v>593.89</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-39.73</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20041029.0</t>
+          <t>18742996.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>35789543.06</t>
+          <t>28629095.72</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1976159.79</v>
+        <v>-2010495.7</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-457226.67</v>
+        <v>-1976159.79</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1370572.98</v>
+        <v>-457226.67</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>4044016.81</v>
+        <v>1370572.98</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>7481492.25</v>
+        <v>4044016.81</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>10514780.48</v>
+        <v>7481492.25</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>14618542.22</v>
+        <v>10514780.48</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
+          <t>2543942.421289739</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>16243824.98</v>
+        <v>14618542.22</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
+          <t>348560.6398269488</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1710514.65</v>
+        <v>16243824.98</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>546.012</t>
+          <t>523.722</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,97 +9523,97 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-08-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-6.91</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-5.03</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>2.28</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-6.45</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>-5.03</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>2.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -9629,42 +9629,42 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -9674,32 +9674,32 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.43</t>
+          <t>-114.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14095689.0</t>
+          <t>13427032.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12822875.6</t>
+          <t>13469101.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13707477.2</t>
+          <t>13623522.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>38208147.56</t>
+          <t>37794170.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-884601</t>
+          <t>-154420</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2692573.381566256</t>
+          <t>-2541487.422143453</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1866957.84</v>
+        <v>-1710514.65</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>559.794</t>
+          <t>546.012</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.93</t>
+          <t>-115.43</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>158370091.70317</t>
+          <t>158200831.7417266</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14163483.0</t>
+          <t>14095689.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>12156684.4</t>
+          <t>12822875.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15987215.5</t>
+          <t>13707477.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>39179007.58</t>
+          <t>38208147.56</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3830531</t>
+          <t>-884601</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2842685.298585612</t>
+          <t>-2692573.381566256</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2095412.87</v>
+        <v>-1866957.84</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI23"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4580.6</t>
+          <t>3567.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1994.96</t>
+          <t>2036.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>139.36</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>295.4730432735587</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>81.12187788900792</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>3041</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-43.77</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-43.90</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>9.74</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>41.15</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>40.95</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1339,12 +1349,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4583.4</t>
+          <t>4580.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1978.44</t>
+          <t>1994.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>428.66</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>334.4459824343861</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>139.3640774002943</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>1071</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-43.63</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-43.77</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>41.05</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>502.85</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>369.9154197133118</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>428.6613596521215</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>4093</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-43.90</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-43.63</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>41.15</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>377.12</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>359.2343397244373</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>502.8481428814416</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>6088</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-44.25</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-43.90</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>40.95</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,59 +2778,59 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>456.51</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>333.1227391504366</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>377.1203995347046</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>3545</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-42.53</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-44.25</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>40.7</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>64.93000000000001</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>325.1231645351152</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>456.5050376274121</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>8106</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-40.41</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-42.53</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>41.95</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,175 +3720,175 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>255.47</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>301.2355512456066</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>64.92934070172942</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1085</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>-40.41</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>9.74</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>43.75</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,20 +3898,25 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,12 +4045,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4031,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>449.86</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>344.2003167990389</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>255.4665829256933</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1726</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-40.14</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-40.41</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,27 +4507,27 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4492,42 +4537,42 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>359.64</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>360.333722957829</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>449.8602652840095</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>5010</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-40.21</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-40.14</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>9.74</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>43.7</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>510.95</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>344.0561698076144</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>359.6419448928891</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>2275</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-40.27</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-40.21</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>43.7</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,67 +5379,67 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.88</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,177 +5464,177 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7695.998552821997</t>
+          <t>7691.468930635838</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4967.0</t>
+          <t>3348.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4262.0</t>
+          <t>4081.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2968.4</t>
+          <t>3197.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1384.28</t>
+          <t>1444.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>884</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>310.3628294939249</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>593.89</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>341.2223925193826</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>510.9499891593996</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>3348</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/02/13</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-40.14</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-40.27</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>晶達</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-7.735853911671112</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-4.485033608893704</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-10.68337399707084</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>9.76</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>6.98</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>22.26</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>30.85%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>6.90%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>高亮度液晶面板模組44.83%、高亮度液晶顯示器32.63%、工業用主機板11.36%、其他10.85%、特殊應用系統平臺0.33% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>晶達-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>43.7</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
           <t>43.7</t>
@@ -5587,20 +5642,25 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>20.93</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 顯示器模組、監視器/顯示器** 觸控面板 - 觸控面板、公共資訊查詢站(Kiosk)、金融提款機(ATM)、自動售票機</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5619,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,67 +5810,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5820,7 +5880,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,198 +5900,203 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>18742996.0</t>
+          <t>19510303.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>28629095.72</t>
+          <t>27612703.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-2010495.7</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1089746.737891086</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-2336902.323336951</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>22454494</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>5.48</t>
-        </is>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM13" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
         <is>
           <t>26.45</t>
         </is>
       </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CH13" t="inlineStr">
         <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6050,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,198 +6336,203 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>20041029.0</t>
+          <t>18742996.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>35789543.06</t>
+          <t>28629095.72</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>-1976159.79</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1712773.839932547</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-2010495.702555094</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>27156279</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM14" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
+          <t>26.95</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6481,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,198 +6772,203 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>-457226.67</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>2389731.938566664</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-1976159.790632617</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>14096102</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ15" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>26.05</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
+          <t>26.35</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6912,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,198 +7208,203 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>1370572.98</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>3183530.434784716</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-457226.6739350557</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>17441489</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
+      <c r="BH16" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ16" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR16" t="inlineStr">
+      <c r="BS16" t="inlineStr">
         <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
       <c r="BT16" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
-      </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
+          <t>25.75</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>26.1</t>
         </is>
       </c>
-      <c r="CG16" t="inlineStr">
+      <c r="CH16" t="inlineStr">
         <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7343,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,198 +7644,203 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>4044016.81</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>3845486.272733765</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1370572.98113057</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>16403151</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ17" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV17" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>26.3</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7774,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,198 +8080,203 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>7481492.25</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>4295470.50757071</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>4044016.810469657</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>18617959</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV18" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8205,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,172 +8516,172 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>10514780.48</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>4341189.361589083</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>7481492.252008721</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>33646444</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>5.48</t>
-        </is>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK19" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM19" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV19" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
       <c r="CD19" t="inlineStr">
         <is>
           <t>27.1</t>
@@ -8599,25 +8689,30 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8636,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,198 +8952,203 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>14618542.22</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>3770225.199694605</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>10514780.48092137</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>32283584</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>5.48</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV20" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
         <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
+          <t>26.95</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9067,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,198 +9388,203 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>16243824.98</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>2543942.421289739</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>14618542.21933509</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>66958254</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BL21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV21" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>27.75</t>
-        </is>
-      </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9498,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,198 +9824,203 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>158200831.7417266</t>
+          <t>158021925.0021552</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-1710514.65</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>348560.6398269488</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>16243824.98066416</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>250787919</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>三商電</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BM22" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ22" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV22" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>25.75</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9929,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>546.012</t>
+          <t>523.722</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,12 +10149,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -10060,288 +10170,293 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>843</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-3.29</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>25.54</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>25.72</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>27.73</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>14.49</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-114.89</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>158021925.0021552</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>13427032.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>13469101.4</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>13623522.0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>37794170.94</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-154420</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-2541487.422143453</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-1710514.645318033</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>13427032</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-4.06</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.78</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>26.87</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>12.81</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-115.43</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>158200831.7417266</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>14095689.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>12822875.6</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>13707477.2</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>38208147.56</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-884601</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-2692573.381566256</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-1866957.84</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
+      <c r="BN23" t="inlineStr">
         <is>
           <t>298.8215518698245</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>224.5227559584907</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>40.88738708368201</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
       <c r="BQ23" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
+      <c r="BS23" t="inlineStr">
         <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>17.73</t>
-        </is>
-      </c>
       <c r="BV23" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
           <t>38.02%</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>4.37%</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
           <t>系統整合服務50.29%、維修及保養服務31.33%、金融自動化服務機器18.38% (2024年)</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>三商電-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 觸控面板 - 金融提款機(ATM)、自動售票機** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3567.6</t>
+          <t>3256.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2036.44</t>
+          <t>2072.16</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3041</v>
+        <v>1988</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4580.6</t>
+          <t>3567.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1994.96</t>
+          <t>2036.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1071</v>
+        <v>3041</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4583.4</t>
+          <t>4580.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1978.44</t>
+          <t>1994.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4093</v>
+        <v>1071</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6088</v>
+        <v>4093</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3545</v>
+        <v>6088</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,59 +3214,59 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>8106</v>
+        <v>3545</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>64.92934070172942</t>
+          <t>456.5050376274121</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1085</v>
+        <v>8106</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>255.4665829256933</t>
+          <t>64.92934070172942</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1726</v>
+        <v>1085</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>449.8602652840095</t>
+          <t>255.4665829256933</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5010</v>
+        <v>1726</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,27 +4943,27 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,42 +4973,42 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>359.6419448928891</t>
+          <t>449.8602652840095</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2275</v>
+        <v>5010</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>47.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7691.468930635838</t>
+          <t>7684.67316017316</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3348.0</t>
+          <t>2275.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4081.4</t>
+          <t>3945.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3197.2</t>
+          <t>3247.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1444.32</t>
+          <t>1469.42</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>697</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>341.2223925193826</t>
+          <t>344.0561698076144</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>510.9499891593996</t>
+          <t>359.6419448928891</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>3348</v>
+        <v>2275</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>19510303.0</t>
+          <t>19145978.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27612703.3</t>
+          <t>27156087.18</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>22454494</v>
+        <v>14581530</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,102 +6140,102 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-60.97</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-08-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-5.03</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>-1.89</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-61.81</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-2.00</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-5.03</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>4.41</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.78</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,67 +6246,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>18742996.0</t>
+          <t>19510303.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28629095.72</t>
+          <t>27612703.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>27156279</v>
+        <v>22454494</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20041029.0</t>
+          <t>18742996.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>35789543.06</t>
+          <t>28629095.72</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>14096102</v>
+        <v>27156279</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>17441489</v>
+        <v>14096102</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>16403151</v>
+        <v>17441489</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>18617959</v>
+        <v>16403151</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>7481492.252008721</t>
+          <t>4044016.810469657</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>33646444</v>
+        <v>18617959</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>10514780.48092137</t>
+          <t>7481492.252008721</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>32283584</v>
+        <v>33646444</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>14618542.21933509</t>
+          <t>10514780.48092137</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>66958254</v>
+        <v>32283584</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
+          <t>2543942.421289739</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>16243824.98066416</t>
+          <t>14618542.21933509</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>250787919</v>
+        <v>66958254</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>523.722</t>
+          <t>9072.488</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>67.84</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>548</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-114.89</t>
+          <t>-113.46</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>158021925.0021552</t>
+          <t>157826588.3737446</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13427032.0</t>
+          <t>250787919.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>13469101.4</t>
+          <t>61475632.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13623522.0</t>
+          <t>36628463.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>37794170.94</t>
+          <t>41978510.2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-154420</t>
+          <t>24847169</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2541487.422143453</t>
+          <t>348560.6398269488</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1710514.645318033</t>
+          <t>16243824.98066416</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>13427032</v>
+        <v>250787919</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3256.2</t>
+          <t>2755.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2072.16</t>
+          <t>2129.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1988</v>
+        <v>3586</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3567.6</t>
+          <t>3256.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2036.44</t>
+          <t>2072.16</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3041</v>
+        <v>1988</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4580.6</t>
+          <t>3567.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1994.96</t>
+          <t>2036.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1071</v>
+        <v>3041</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4583.4</t>
+          <t>4580.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1978.44</t>
+          <t>1994.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4093</v>
+        <v>1071</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6088</v>
+        <v>4093</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>3545</v>
+        <v>6088</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,59 +3650,59 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>8106</v>
+        <v>3545</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>64.92934070172942</t>
+          <t>456.5050376274121</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1085</v>
+        <v>8106</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>255.4665829256933</t>
+          <t>64.92934070172942</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1726</v>
+        <v>1085</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>449.8602652840095</t>
+          <t>255.4665829256933</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>5010</v>
+        <v>1726</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.46</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,27 +5379,27 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>21.71</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5409,42 +5409,42 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-112.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7684.67316017316</t>
+          <t>7681.350864553315</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2275.0</t>
+          <t>5010.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3945.2</t>
+          <t>3903.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3247.3</t>
+          <t>3437.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1469.42</t>
+          <t>1555.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>465</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>344.0561698076144</t>
+          <t>360.333722957829</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>359.6419448928891</t>
+          <t>449.8602652840095</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2275</v>
+        <v>5010</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-40.14</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>19145978.8</t>
+          <t>17530372.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27156087.18</t>
+          <t>25677675.12</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14581530</v>
+        <v>9363458</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>19510303.0</t>
+          <t>19145978.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27612703.3</t>
+          <t>27156087.18</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>22454494</v>
+        <v>14581530</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,67 +6682,67 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>18742996.0</t>
+          <t>19510303.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>28629095.72</t>
+          <t>27612703.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>27156279</v>
+        <v>22454494</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20041029.0</t>
+          <t>18742996.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>35789543.06</t>
+          <t>28629095.72</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>14096102</v>
+        <v>27156279</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>17441489</v>
+        <v>14096102</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>16403151</v>
+        <v>17441489</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,17 +8248,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>18617959</v>
+        <v>16403151</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>7481492.252008721</t>
+          <t>4044016.810469657</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>33646444</v>
+        <v>18617959</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>10514780.48092137</t>
+          <t>7481492.252008721</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>32283584</v>
+        <v>33646444</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>14618542.21933509</t>
+          <t>10514780.48092137</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>66958254</v>
+        <v>32283584</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9072.488</t>
+          <t>2501.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-113.46</t>
+          <t>-111.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157826588.3737446</t>
+          <t>157620597.8273639</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>250787919.0</t>
+          <t>66958254.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>61475632.4</t>
+          <t>71886475.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>36628463.0</t>
+          <t>41568300.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>41978510.2</t>
+          <t>42670245.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>24847169</t>
+          <t>30318174</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>348560.6398269488</t>
+          <t>2543942.421289739</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>16243824.98066416</t>
+          <t>14618542.21933509</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>250787919</v>
+        <v>66958254</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-43.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-118.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2755.8</t>
+          <t>2757.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3432.9</t>
+          <t>3670.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2129.54</t>
+          <t>2178.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-677</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>205.4867816696991</t>
+          <t>182.9100767412474</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5.025251621802454</t>
+          <t>58.73819963476308</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3586</v>
+        <v>4102</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-44.11</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>40.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>40.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3256.2</t>
+          <t>2755.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2072.16</t>
+          <t>2129.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1988</v>
+        <v>3586</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3567.6</t>
+          <t>3256.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2036.44</t>
+          <t>2072.16</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3041</v>
+        <v>1988</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4580.6</t>
+          <t>3567.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1994.96</t>
+          <t>2036.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1071</v>
+        <v>3041</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4583.4</t>
+          <t>4580.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1978.44</t>
+          <t>1994.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>4093</v>
+        <v>1071</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4110.0</t>
+          <t>4583.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1897.56</t>
+          <t>1978.44</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>6088</v>
+        <v>4093</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3894.4</t>
+          <t>4110.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1788.38</t>
+          <t>1897.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>3545</v>
+        <v>6088</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,59 +4086,59 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>45.57</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3640.4</t>
+          <t>3894.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1742.88</t>
+          <t>1788.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>8106</v>
+        <v>3545</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>43.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.72</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2688.8</t>
+          <t>3640.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1592.36</t>
+          <t>1742.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>64.92934070172942</t>
+          <t>456.5050376274121</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1085</v>
+        <v>8106</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3465.2</t>
+          <t>2688.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1578.56</t>
+          <t>1592.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>255.4665829256933</t>
+          <t>64.92934070172942</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1726</v>
+        <v>1085</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-39.67</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.47</t>
+          <t>-112.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7681.350864553315</t>
+          <t>7679.151798561152</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5010.0</t>
+          <t>1726.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3903.4</t>
+          <t>3465.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3437.6</t>
+          <t>3502.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1555.92</t>
+          <t>1578.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-37</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>360.333722957829</t>
+          <t>344.2003167990389</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>449.8602652840095</t>
+          <t>255.4665829256933</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>5010</v>
+        <v>1726</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-40.14</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>351.187</t>
+          <t>5464.202</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,57 +5810,57 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5870,17 +5870,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2443.17</t>
+          <t>431.15</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-100.12</t>
+          <t>-98.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>17530372.6</t>
+          <t>45377257.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20604449.0</t>
+          <t>32709143.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25677675.12</t>
+          <t>27633591.24</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3074076</t>
+          <t>12668114</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-229711.4704283447</t>
+          <t>784088.3793443948</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3943730.245830517</t>
+          <t>6359987.553094462</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>9363458</v>
+        <v>153330525</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>19145978.8</t>
+          <t>17530372.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27156087.18</t>
+          <t>25677675.12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>14581530</v>
+        <v>9363458</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6499,27 +6499,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19510303.0</t>
+          <t>19145978.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>27612703.3</t>
+          <t>27156087.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>22454494</v>
+        <v>14581530</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6935,27 +6935,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,67 +7118,67 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18742996.0</t>
+          <t>19510303.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28629095.72</t>
+          <t>27612703.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>27156279</v>
+        <v>22454494</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20041029.0</t>
+          <t>18742996.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>35789543.06</t>
+          <t>28629095.72</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>14096102</v>
+        <v>27156279</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7807,27 +7807,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23678525.4</t>
+          <t>20041029.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>37885324.3</t>
+          <t>35789543.06</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>17441489</v>
+        <v>14096102</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8243,27 +8243,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>33581878.4</t>
+          <t>23678525.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>39069391.12</t>
+          <t>37885324.3</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>16403151</v>
+        <v>17441489</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8679,22 +8679,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>80458832.0</t>
+          <t>33581878.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>40740037.7</t>
+          <t>39069391.12</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>18617959</v>
+        <v>16403151</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9115,27 +9115,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.91</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>79420646.6</t>
+          <t>80458832.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>41856955.28</t>
+          <t>40740037.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>7481492.252008721</t>
+          <t>4044016.810469657</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>33646444</v>
+        <v>18617959</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9551,27 +9551,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.91</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>75510495.6</t>
+          <t>79420646.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>42296002.84</t>
+          <t>41856955.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>10514780.48092137</t>
+          <t>7481492.252008721</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>32283584</v>
+        <v>33646444</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9987,27 +9987,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2501.8</t>
+          <t>1199.147</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.86</t>
+          <t>-109.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157620597.8273639</t>
+          <t>157724138.8712446</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>66958254.0</t>
+          <t>32283584.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>71886475.4</t>
+          <t>75510495.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41568300.9</t>
+          <t>43833590.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>42670245.7</t>
+          <t>42296002.84</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>30318174</t>
+          <t>31676905</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>2543942.421289739</t>
+          <t>3770225.199694605</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>14618542.21933509</t>
+          <t>10514780.48092137</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>66958254</v>
+        <v>32283584</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10423,27 +10423,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
+          <t>資訊服務業右上上市</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>40.79</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>42.49</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>44.58</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44.58</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4102.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2757.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>2757.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>3670.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2178.26</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2178.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>58.73819963476308</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4102</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4102.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>40.86</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>42.65</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.71</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3586.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2755.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2755.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3432.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2129.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2129.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-5.025251621802454</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3586</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3586.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>40.92</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>42.82</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1988.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3256.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3256.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3575.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2072.16</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2072.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-40.65070871611761</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1988</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1988.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>40.96</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.99</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3041.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3567.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3567.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>3604.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2036.44</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2036.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>81.12187788900792</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3041</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3041.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>41.16</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>43.16</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>45.13</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>45.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1071.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4580.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4580.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>3634.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1994.96</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1994.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>139.3640774002943</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1071</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1071.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>41.65000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>43.33</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>45.28</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>45.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>4093.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4583.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>4583.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>4024.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1978.44</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1978.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>428.6613596521215</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>4093</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4093.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>42.12</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>45.42</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>45.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6088.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4110.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4110</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>4006.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1897.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1897.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>502.8481428814416</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6088</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6088.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>43.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>45.57</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3545.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3894.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3894.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3919.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1788.38</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1788.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>377.1203995347046</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3545</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3545.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>43.96</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>45.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>45.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8106.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3640.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3640.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3860.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1742.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1742.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>456.5050376274121</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8106</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8106.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.59</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>44.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.85</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1085.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2688.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>2688.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>3475.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1592.36</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1592.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>64.92934070172942</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1085</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1085.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>43.63</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1726.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3465.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3465.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3502.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1578.56</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1578.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>255.4665829256933</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1726</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1726.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>27.01</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>26.31</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>26.44</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26.44</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>153330525.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>45377257.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>45377257.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>32709143.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>27633591.24</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>27633591.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>6359987.553094462</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>153330525</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>153330525.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>26.59</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>26.17</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>26.42</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>26.42</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>9363458.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>17530372.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>17530372.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>20604449.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>25677675.12</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>25677675.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3943730.245830517</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>9363458</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>9363458.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>26.48</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>26.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>26.45</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14581530.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>19145978.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>19145978.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>26363928.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>27156087.18</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>27156087.18</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3097436.699800827</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14581530</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14581530.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>26.39</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>26.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>22454494.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>19510303.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>19510303</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>49984567.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>27612703.3</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>27612703.3</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2336902.323336951</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>22454494</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>22454494.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>26.38</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>26.06</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>26.52</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>26.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>27156279.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>18742996.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>18742996</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>49081821.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>28629095.72</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>28629095.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-2010495.702555094</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>27156279</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>27156279.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>26.31</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>26.02</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>26.57</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>14096102.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>20041029.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>20041029</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>47775762.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>35789543.06</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>35789543.06</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1976159.790632617</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>14096102</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>14096102.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>26.43</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>25.99</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>26.62</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26.62</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>17441489.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>23678525.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>23678525.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>47782500.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>37885324.3</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>37885324.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-457226.6739350557</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>17441489</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>17441489.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>26.51</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>26.64</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>26.64</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>16403151.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>33581878.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>33581878.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>47528755.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>39069391.12</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>39069391.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1370572.98113057</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>16403151</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>16403151.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>26.71</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>26.67</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>26.67</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>18617959.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>80458832.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>80458832</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>46963966.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>40740037.7</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>40740037.7</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>4044016.810469657</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>18617959</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>18617959.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>26.55</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.91</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>26.71</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>26.71</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>33646444.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>79420646.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>79420646.59999999</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>46121761.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>41856955.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>41856955.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>7481492.252008721</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>33646444</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>33646444.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>26.38</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>26.73</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>26.73</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>32283584.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>75510495.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>75510495.59999999</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>43833590.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>42296002.84</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>42296002.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>10514780.48092137</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>32283584</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>32283584.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1049,38 +1049,38 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>42.49</v>
+        <v>42.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.58</v>
+        <v>44.45</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.05</t>
+          <t>-118.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2757.6</v>
+        <v>3214.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3670.5</t>
+          <t>3897.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2178.26</v>
+        <v>2233.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-683</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>182.9100767412474</t>
+          <t>161.8283973231309</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>58.73819963476308</t>
+          <t>45.8791605234901</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-43.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.65</v>
+        <v>42.49</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.71</v>
+        <v>44.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-118.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2755.8</v>
+        <v>2757.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3432.9</t>
+          <t>3670.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2129.54</v>
+        <v>2178.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-677</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>205.4867816696991</t>
+          <t>182.9100767412474</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5.025251621802454</t>
+          <t>58.73819963476308</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-44.11</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>40.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>40.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.82</v>
+        <v>42.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.84</v>
+        <v>44.71</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3256.2</v>
+        <v>2755.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2072.16</v>
+        <v>2129.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43</v>
+        <v>42.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.99</v>
+        <v>44.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3567.6</v>
+        <v>3256.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2036.44</v>
+        <v>2072.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.16</v>
+        <v>43</v>
       </c>
       <c r="AN6" t="n">
-        <v>45.13</v>
+        <v>44.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4580.6</v>
+        <v>3567.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1994.96</v>
+        <v>2036.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.33</v>
+        <v>43.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4583.4</v>
+        <v>4580.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1978.44</v>
+        <v>1994.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>41.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.5</v>
+        <v>43.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.42</v>
+        <v>45.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4110</v>
+        <v>4583.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1897.56</v>
+        <v>1978.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>60.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.72</v>
+        <v>43.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.57</v>
+        <v>45.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3894.4</v>
+        <v>4110</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1788.38</v>
+        <v>1897.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,55 +4474,55 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.96</v>
+        <v>43.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.72</v>
+        <v>45.57</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3640.4</v>
+        <v>3894.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1742.88</v>
+        <v>1788.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>44.14</v>
+        <v>43.96</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.85</v>
+        <v>45.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2688.8</v>
+        <v>3640.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1592.36</v>
+        <v>1742.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>64.92934070172942</t>
+          <t>456.5050376274121</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-22.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>44.26</v>
+        <v>44.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.96</v>
+        <v>45.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.27</t>
+          <t>-112.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7679.151798561152</t>
+          <t>7675.349137931034</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3465.2</v>
+        <v>2688.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3502.3</t>
+          <t>3475.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1578.56</v>
+        <v>1592.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-37</t>
+          <t>-786</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>344.2003167990389</t>
+          <t>301.2355512456066</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>255.4665829256933</t>
+          <t>64.92934070172942</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1726.0</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5464.202</t>
+          <t>5342.422</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>26.31</v>
+        <v>26.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>26.44</v>
+        <v>26.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>431.15</t>
+          <t>233.09</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-98.40</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>45377257.2</v>
+        <v>70442197.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>32709143.1</t>
+          <t>44592596.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>27633591.24</v>
+        <v>30181049.5</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>12668114</t>
+          <t>25849600</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>784088.3793443948</t>
+          <t>2717286.24767827</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6359987.553094462</t>
+          <t>13349874.52351458</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>351.187</t>
+          <t>5464.202</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,54 +6174,54 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>26.17</v>
+        <v>26.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,17 +6230,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2443.17</t>
+          <t>431.15</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-100.12</t>
+          <t>-98.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>17530372.6</v>
+        <v>45377257.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20604449.0</t>
+          <t>32709143.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>25677675.12</v>
+        <v>27633591.24</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3074076</t>
+          <t>12668114</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-229711.4704283447</t>
+          <t>784088.3793443948</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3943730.245830517</t>
+          <t>6359987.553094462</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>26.12</v>
+        <v>26.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>19145978.8</v>
+        <v>17530372.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>27156087.18</v>
+        <v>25677675.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>26.1</v>
+        <v>26.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.48</v>
+        <v>26.45</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>19510303</v>
+        <v>19145978.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>27612703.3</v>
+        <v>27156087.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,63 +7464,63 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>26.06</v>
+        <v>26.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.52</v>
+        <v>26.48</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>18742996</v>
+        <v>19510303</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>28629095.72</v>
+        <v>27612703.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>26.02</v>
+        <v>26.06</v>
       </c>
       <c r="AN18" t="n">
-        <v>26.57</v>
+        <v>26.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>20041029</v>
+        <v>18742996</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>35789543.06</v>
+        <v>28629095.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>25.99</v>
+        <v>26.02</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.62</v>
+        <v>26.57</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>23678525.4</v>
+        <v>20041029</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37885324.3</v>
+        <v>35789543.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.97</v>
+        <v>25.99</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.64</v>
+        <v>26.62</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>33581878.4</v>
+        <v>23678525.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>39069391.12</v>
+        <v>37885324.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.94</v>
+        <v>25.97</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.67</v>
+        <v>26.64</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>80458832</v>
+        <v>33581878.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>40740037.7</v>
+        <v>39069391.12</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.91</v>
+        <v>25.94</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.71</v>
+        <v>26.67</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>79420646.59999999</v>
+        <v>80458832</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>41856955.28</v>
+        <v>40740037.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>7481492.252008721</t>
+          <t>4044016.810469657</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1199.147</t>
+          <t>1249.932</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.86</v>
+        <v>25.91</v>
       </c>
       <c r="AN23" t="n">
-        <v>26.73</v>
+        <v>26.71</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>89.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.95</t>
+          <t>-108.13</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157724138.8712446</t>
+          <t>157825563.6321429</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>75510495.59999999</v>
+        <v>79420646.59999999</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>43833590.0</t>
+          <t>46121761.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>42296002.84</v>
+        <v>41856955.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>31676905</t>
+          <t>33298885</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>3770225.199694605</t>
+          <t>4341189.361589083</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>10514780.48092137</t>
+          <t>7481492.252008721</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>32283584.0</t>
+          <t>33646444.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>346.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.41</t>
+          <t>-43.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>42.36</v>
+        <v>42.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.45</v>
+        <v>44.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.29</t>
+          <t>-118.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3214.4</v>
+        <v>5436</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3897.5</t>
+          <t>4501.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2233.16</v>
+        <v>2505.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-683</t>
+          <t>934</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>161.8283973231309</t>
+          <t>266.9749291399588</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>45.8791605234901</t>
+          <t>845.2808541325121</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-44.11</t>
+          <t>-43.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,32 +1444,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1479,38 +1479,38 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.49</v>
+        <v>42.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.58</v>
+        <v>44.45</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.05</t>
+          <t>-118.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2757.6</v>
+        <v>3214.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3670.5</t>
+          <t>3897.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2178.26</v>
+        <v>2233.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-683</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>182.9100767412474</t>
+          <t>161.8283973231309</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>58.73819963476308</t>
+          <t>45.8791605234901</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-43.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.65</v>
+        <v>42.49</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.71</v>
+        <v>44.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-118.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2755.8</v>
+        <v>2757.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3432.9</t>
+          <t>3670.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2129.54</v>
+        <v>2178.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-677</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>205.4867816696991</t>
+          <t>182.9100767412474</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5.025251621802454</t>
+          <t>58.73819963476308</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-44.11</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>40.8</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>40.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>42.82</v>
+        <v>42.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.84</v>
+        <v>44.71</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3256.2</v>
+        <v>2755.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2072.16</v>
+        <v>2129.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43</v>
+        <v>42.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.99</v>
+        <v>44.84</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3567.6</v>
+        <v>3256.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2036.44</v>
+        <v>2072.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.16</v>
+        <v>43</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.13</v>
+        <v>44.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4580.6</v>
+        <v>3567.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1994.96</v>
+        <v>2036.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.33</v>
+        <v>43.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4583.4</v>
+        <v>4580.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1978.44</v>
+        <v>1994.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.5</v>
+        <v>43.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.42</v>
+        <v>45.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4110</v>
+        <v>4583.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1897.56</v>
+        <v>1978.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.72</v>
+        <v>43.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.57</v>
+        <v>45.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3894.4</v>
+        <v>4110</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1788.38</v>
+        <v>1897.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,55 +4904,55 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.96</v>
+        <v>43.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.72</v>
+        <v>45.57</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3640.4</v>
+        <v>3894.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1742.88</v>
+        <v>1788.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.63</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.67</t>
+          <t>-41.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>56.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.26000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>44.14</v>
+        <v>43.96</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.85</v>
+        <v>45.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.04</t>
+          <t>-112.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7675.349137931034</t>
+          <t>7694.786944045911</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2688.8</v>
+        <v>3640.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3475.4</t>
+          <t>3860.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1592.36</v>
+        <v>1742.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-786</t>
+          <t>-220</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>301.2355512456066</t>
+          <t>325.1231645351152</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>64.92934070172942</t>
+          <t>456.5050376274121</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>8106.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-40.41</t>
+          <t>-42.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1967.848</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5342.422</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,94 +5723,94 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.62</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>26.44</v>
+        <v>26.58</v>
       </c>
       <c r="AN13" t="n">
-        <v>26.46</v>
+        <v>26.48</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>233.09</t>
+          <t>151.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-93.83</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>70442197.59999999</v>
+        <v>77090781.40000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>44592596.8</t>
+          <t>48300542.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>30181049.5</v>
+        <v>30876711.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>25849600</t>
+          <t>28790239</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2717286.24767827</t>
+          <t>3937746.969530968</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>13349874.52351458</t>
+          <t>10650280.93972081</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5464.202</t>
+          <t>5342.422</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>26.31</v>
+        <v>26.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.44</v>
+        <v>26.46</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>431.15</t>
+          <t>233.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-98.40</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>45377257.2</v>
+        <v>70442197.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32709143.1</t>
+          <t>44592596.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>27633591.24</v>
+        <v>30181049.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>12668114</t>
+          <t>25849600</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>784088.3793443948</t>
+          <t>2717286.24767827</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6359987.553094462</t>
+          <t>13349874.52351458</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>351.187</t>
+          <t>5464.202</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,54 +6604,54 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>26.17</v>
+        <v>26.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,17 +6660,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2443.17</t>
+          <t>431.15</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-100.12</t>
+          <t>-98.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>17530372.6</v>
+        <v>45377257.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>20604449.0</t>
+          <t>32709143.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>25677675.12</v>
+        <v>27633591.24</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3074076</t>
+          <t>12668114</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-229711.4704283447</t>
+          <t>784088.3793443948</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3943730.245830517</t>
+          <t>6359987.553094462</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6736,17 +6736,17 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>26.12</v>
+        <v>26.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>19145978.8</v>
+        <v>17530372.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>27156087.18</v>
+        <v>25677675.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>26.1</v>
+        <v>26.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.48</v>
+        <v>26.45</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>19510303</v>
+        <v>19145978.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>27612703.3</v>
+        <v>27156087.18</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7596,17 +7596,17 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,63 +7894,63 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>26.06</v>
+        <v>26.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>26.52</v>
+        <v>26.48</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>18742996</v>
+        <v>19510303</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28629095.72</v>
+        <v>27612703.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>26.02</v>
+        <v>26.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.57</v>
+        <v>26.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>20041029</v>
+        <v>18742996</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>35789543.06</v>
+        <v>28629095.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8456,17 +8456,17 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.99</v>
+        <v>26.02</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.62</v>
+        <v>26.57</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>23678525.4</v>
+        <v>20041029</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>37885324.3</v>
+        <v>35789543.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8886,17 +8886,17 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.97</v>
+        <v>25.99</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.64</v>
+        <v>26.62</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>33581878.4</v>
+        <v>23678525.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>39069391.12</v>
+        <v>37885324.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.94</v>
+        <v>25.97</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.67</v>
+        <v>26.64</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>80458832</v>
+        <v>33581878.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>40740037.7</v>
+        <v>39069391.12</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9746,17 +9746,17 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1249.932</t>
+          <t>704.739</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>73.53</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.91</v>
+        <v>25.94</v>
       </c>
       <c r="AN23" t="n">
-        <v>26.71</v>
+        <v>26.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>96.54</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.13</t>
+          <t>-106.55</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157825563.6321429</t>
+          <t>157719601.5149786</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>79420646.59999999</v>
+        <v>80458832</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>46121761.1</t>
+          <t>46963966.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>41856955.28</v>
+        <v>40740037.7</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>33298885</t>
+          <t>33494865</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>4341189.361589083</t>
+          <t>4295470.50757071</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>7481492.252008721</t>
+          <t>4044016.810469657</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>33646444.0</t>
+          <t>18617959.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10176,17 +10176,17 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>23.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.27</t>
+          <t>-43.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>42.19</v>
+        <v>42.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.31</v>
+        <v>44.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.34</t>
+          <t>-118.16</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5436</v>
+        <v>5212</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4501.8</t>
+          <t>4234.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2505.62</v>
+        <v>2509.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>977</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>266.9749291399588</t>
+          <t>285.5410967038906</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>845.2808541325121</t>
+          <t>387.6550183055151</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>-43.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.41</t>
+          <t>-43.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.36</v>
+        <v>42.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.45</v>
+        <v>44.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.29</t>
+          <t>-118.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3214.4</v>
+        <v>5436</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3897.5</t>
+          <t>4501.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2233.16</v>
+        <v>2505.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-683</t>
+          <t>934</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>161.8283973231309</t>
+          <t>266.9749291399588</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>45.8791605234901</t>
+          <t>845.2808541325121</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-44.11</t>
+          <t>-43.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,32 +1874,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1909,38 +1909,38 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.49</v>
+        <v>42.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.58</v>
+        <v>44.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.05</t>
+          <t>-118.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2757.6</v>
+        <v>3214.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3670.5</t>
+          <t>3897.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2178.26</v>
+        <v>2233.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-683</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>182.9100767412474</t>
+          <t>161.8283973231309</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>58.73819963476308</t>
+          <t>45.8791605234901</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-43.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>42.65</v>
+        <v>42.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.71</v>
+        <v>44.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-118.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2755.8</v>
+        <v>2757.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3432.9</t>
+          <t>3670.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2129.54</v>
+        <v>2178.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-677</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>205.4867816696991</t>
+          <t>182.9100767412474</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5.025251621802454</t>
+          <t>58.73819963476308</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-44.11</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>40.8</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>40.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>42.82</v>
+        <v>42.65</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.84</v>
+        <v>44.71</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3256.2</v>
+        <v>2755.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2072.16</v>
+        <v>2129.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43</v>
+        <v>42.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.99</v>
+        <v>44.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3567.6</v>
+        <v>3256.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2036.44</v>
+        <v>2072.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.16</v>
+        <v>43</v>
       </c>
       <c r="AN8" t="n">
-        <v>45.13</v>
+        <v>44.99</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4580.6</v>
+        <v>3567.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1994.96</v>
+        <v>2036.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.33</v>
+        <v>43.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4583.4</v>
+        <v>4580.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1978.44</v>
+        <v>1994.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.5</v>
+        <v>43.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.42</v>
+        <v>45.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4110</v>
+        <v>4583.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1897.56</v>
+        <v>1978.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.72</v>
+        <v>43.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.57</v>
+        <v>45.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3894.4</v>
+        <v>4110</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1788.38</v>
+        <v>1897.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-41.82</t>
+          <t>-43.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,55 +5334,55 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.26000000000001</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.96</v>
+        <v>43.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.72</v>
+        <v>45.57</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.77</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.20</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7694.786944045911</t>
+          <t>7685.628223495703</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3640.4</v>
+        <v>3894.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3860.9</t>
+          <t>3919.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1742.88</v>
+        <v>1788.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-220</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>325.1231645351152</t>
+          <t>333.1227391504366</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>456.5050376274121</t>
+          <t>377.1203995347046</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>8106.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1967.848</t>
+          <t>13163.227</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,64 +5628,64 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.45</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-08-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>28.3</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>59.61</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>27.5</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>57.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>93.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>26.58</v>
+        <v>26.76</v>
       </c>
       <c r="AN13" t="n">
-        <v>26.48</v>
+        <v>26.52</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>151.69</t>
+          <t>124.40</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-93.83</t>
+          <t>-91.05</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>55697413.0</t>
+          <t>382436650.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>77090781.40000001</v>
+        <v>150661805.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>48300542.2</t>
+          <t>84903892.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>30876711.56</v>
+        <v>38204311.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>28790239</t>
+          <t>65757913</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3937746.969530968</t>
+          <t>8408824.540768072</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>10650280.93972081</t>
+          <t>32999751.18257214</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>55697413.0</t>
+          <t>382436650.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>28.55</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>28.1</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5342.422</t>
+          <t>1967.848</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,94 +6153,94 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.62</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>26.44</v>
+        <v>26.58</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.46</v>
+        <v>26.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>233.09</t>
+          <t>151.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-93.83</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>70442197.59999999</v>
+        <v>77090781.40000001</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44592596.8</t>
+          <t>48300542.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>30181049.5</v>
+        <v>30876711.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>25849600</t>
+          <t>28790239</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>2717286.24767827</t>
+          <t>3937746.969530968</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>13349874.52351458</t>
+          <t>10650280.93972081</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5464.202</t>
+          <t>5342.422</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>26.31</v>
+        <v>26.44</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.44</v>
+        <v>26.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>431.15</t>
+          <t>233.09</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-98.40</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>45377257.2</v>
+        <v>70442197.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32709143.1</t>
+          <t>44592596.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>27633591.24</v>
+        <v>30181049.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12668114</t>
+          <t>25849600</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>784088.3793443948</t>
+          <t>2717286.24767827</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6359987.553094462</t>
+          <t>13349874.52351458</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,24 +6856,24 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>28.1</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>28.45</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
       <c r="CH15" t="inlineStr">
         <is>
           <t>16.25</t>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>351.187</t>
+          <t>5464.202</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,54 +7034,54 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>26.17</v>
+        <v>26.31</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2443.17</t>
+          <t>431.15</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-100.12</t>
+          <t>-98.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>17530372.6</v>
+        <v>45377257.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20604449.0</t>
+          <t>32709143.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>25677675.12</v>
+        <v>27633591.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3074076</t>
+          <t>12668114</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-229711.4704283447</t>
+          <t>784088.3793443948</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3943730.245830517</t>
+          <t>6359987.553094462</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>26.12</v>
+        <v>26.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>19145978.8</v>
+        <v>17530372.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>27156087.18</v>
+        <v>25677675.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>26.1</v>
+        <v>26.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>26.48</v>
+        <v>26.45</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>19510303</v>
+        <v>19145978.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>27612703.3</v>
+        <v>27156087.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,63 +8324,63 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>26.06</v>
+        <v>26.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.52</v>
+        <v>26.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>18742996</v>
+        <v>19510303</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28629095.72</v>
+        <v>27612703.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,24 +8576,24 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>26.45</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
       <c r="CH19" t="inlineStr">
         <is>
           <t>16.25</t>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>26.02</v>
+        <v>26.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.57</v>
+        <v>26.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>20041029</v>
+        <v>18742996</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>35789543.06</v>
+        <v>28629095.72</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.99</v>
+        <v>26.02</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.62</v>
+        <v>26.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>23678525.4</v>
+        <v>20041029</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>37885324.3</v>
+        <v>35789543.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.97</v>
+        <v>25.99</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.64</v>
+        <v>26.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>33581878.4</v>
+        <v>23678525.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>39069391.12</v>
+        <v>37885324.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>704.739</t>
+          <t>623.872</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>26.51</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.94</v>
+        <v>25.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>26.67</v>
+        <v>26.64</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>96.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.36</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157719601.5149786</t>
+          <t>158312102.0470085</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>80458832</v>
+        <v>33581878.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>46963966.7</t>
+          <t>47528755.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>40740037.7</v>
+        <v>39069391.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>33494865</t>
+          <t>-13946877</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>4295470.50757071</t>
+          <t>3845486.272733765</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>4044016.810469657</t>
+          <t>1370572.98113057</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>18617959.0</t>
+          <t>16403151.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.10</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.17</v>
+        <v>44.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.16</t>
+          <t>-117.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>868.0</t>
+          <t>6723.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5212</v>
+        <v>5839.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4234.1</t>
+          <t>4297.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2509.54</v>
+        <v>2636.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>285.5410967038906</t>
+          <t>318.0348599446734</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>387.6550183055151</t>
+          <t>496.750557768979</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>868.0</t>
+          <t>6723.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>23.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-43.27</t>
+          <t>-43.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.19</v>
+        <v>42.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.31</v>
+        <v>44.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.34</t>
+          <t>-118.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5436</v>
+        <v>5212</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4501.8</t>
+          <t>4234.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2505.62</v>
+        <v>2509.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>977</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>266.9749291399588</t>
+          <t>285.5410967038906</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>845.2808541325121</t>
+          <t>387.6550183055151</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>-43.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>346.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.41</t>
+          <t>-43.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,63 +1879,63 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.36</v>
+        <v>42.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.45</v>
+        <v>44.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.29</t>
+          <t>-118.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3214.4</v>
+        <v>5436</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3897.5</t>
+          <t>4501.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2233.16</v>
+        <v>2505.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-683</t>
+          <t>934</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>161.8283973231309</t>
+          <t>266.9749291399588</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>45.8791605234901</t>
+          <t>845.2808541325121</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-44.11</t>
+          <t>-43.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,27 +2309,27 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2339,38 +2339,38 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>42.49</v>
+        <v>42.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.58</v>
+        <v>44.45</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.05</t>
+          <t>-118.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2757.6</v>
+        <v>3214.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3670.5</t>
+          <t>3897.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2178.26</v>
+        <v>2233.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-683</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>182.9100767412474</t>
+          <t>161.8283973231309</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>58.73819963476308</t>
+          <t>45.8791605234901</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4102.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-43.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>42.65</v>
+        <v>42.49</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.71</v>
+        <v>44.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.63</t>
+          <t>-118.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2755.8</v>
+        <v>2757.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3432.9</t>
+          <t>3670.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2129.54</v>
+        <v>2178.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-677</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>205.4867816696991</t>
+          <t>182.9100767412474</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5.025251621802454</t>
+          <t>58.73819963476308</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3586.0</t>
+          <t>4102.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-44.11</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>40.55</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>40.8</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>40.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-19.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>40.86</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>42.82</v>
+        <v>42.65</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.84</v>
+        <v>44.71</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.02</t>
+          <t>-117.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3256.2</v>
+        <v>2755.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3575.3</t>
+          <t>3432.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2072.16</v>
+        <v>2129.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>-677</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>243.7616968136085</t>
+          <t>205.4867816696991</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-40.65070871611761</t>
+          <t>-5.025251621802454</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1988.0</t>
+          <t>3586.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-44.52</t>
+          <t>-44.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43</v>
+        <v>42.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.99</v>
+        <v>44.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.43</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-117.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3567.6</v>
+        <v>3256.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3604.0</t>
+          <t>3575.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2036.44</v>
+        <v>2072.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-36</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>295.4730432735587</t>
+          <t>243.7616968136085</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>81.12187788900792</t>
+          <t>-40.65070871611761</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3041.0</t>
+          <t>1988.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-44.52</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.07</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>11.67</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.16</v>
+        <v>43</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.13</v>
+        <v>44.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.59</t>
+          <t>-18.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.53</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4580.6</v>
+        <v>3567.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3634.7</t>
+          <t>3604.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1994.96</v>
+        <v>2036.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>-36</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>334.4459824343861</t>
+          <t>295.4730432735587</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>139.3640774002943</t>
+          <t>81.12187788900792</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1071.0</t>
+          <t>3041.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-43.77</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-42.93</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>41.65000000000001</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.33</v>
+        <v>43.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-21.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-115.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4583.4</v>
+        <v>4580.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4024.3</t>
+          <t>3634.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1978.44</v>
+        <v>1994.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>369.9154197133118</t>
+          <t>334.4459824343861</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>428.6613596521215</t>
+          <t>139.3640774002943</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4093.0</t>
+          <t>1071.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.20</t>
+          <t>-42.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>41.65000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.5</v>
+        <v>43.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.42</v>
+        <v>45.28</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.05</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4110</v>
+        <v>4583.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4006.7</t>
+          <t>4024.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1897.56</v>
+        <v>1978.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>359.2343397244373</t>
+          <t>369.9154197133118</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>502.8481428814416</t>
+          <t>428.6613596521215</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6088.0</t>
+          <t>4093.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-43.90</t>
+          <t>-43.63</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-43.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.72</v>
+        <v>43.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.57</v>
+        <v>45.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-26.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.90</t>
+          <t>-113.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7685.628223495703</t>
+          <t>7689.060085836909</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3894.4</v>
+        <v>4110</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3919.8</t>
+          <t>4006.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1788.38</v>
+        <v>1897.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>333.1227391504366</t>
+          <t>359.2343397244373</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>377.1203995347046</t>
+          <t>502.8481428814416</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>6088.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-43.90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13163.227</t>
+          <t>3587.848</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>81.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>57.30</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>88.18</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>26.76</v>
+        <v>26.91</v>
       </c>
       <c r="AN13" t="n">
-        <v>26.52</v>
+        <v>26.54</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>124.40</t>
+          <t>85.66</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-91.05</t>
+          <t>-88.61</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>382436650.0</t>
+          <t>102246103.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>150661805.4</v>
+        <v>169238334.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>84903892.1</t>
+          <t>93384353.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>38204311.38</v>
+        <v>39767486.3</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>65757913</t>
+          <t>75853980</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>8408824.540768072</t>
+          <t>11239020.08034279</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>32999751.18257214</t>
+          <t>26805095.54800376</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>382436650.0</t>
+          <t>102246103.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1967.848</t>
+          <t>13163.227</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,64 +6058,64 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-08-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>28.3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>59.61</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>27.5</t>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>57.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,17 +6174,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>93.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>26.58</v>
+        <v>26.76</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.48</v>
+        <v>26.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>151.69</t>
+          <t>124.40</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-93.83</t>
+          <t>-91.05</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>55697413.0</t>
+          <t>382436650.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>77090781.40000001</v>
+        <v>150661805.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>48300542.2</t>
+          <t>84903892.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>30876711.56</v>
+        <v>38204311.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>28790239</t>
+          <t>65757913</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3937746.969530968</t>
+          <t>8408824.540768072</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>10650280.93972081</t>
+          <t>32999751.18257214</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>55697413.0</t>
+          <t>382436650.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>28.55</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>28.1</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5342.422</t>
+          <t>1967.848</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,94 +6583,94 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.62</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>26.44</v>
+        <v>26.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.46</v>
+        <v>26.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>233.09</t>
+          <t>151.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-93.83</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>70442197.59999999</v>
+        <v>77090781.40000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44592596.8</t>
+          <t>48300542.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>30181049.5</v>
+        <v>30876711.56</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>25849600</t>
+          <t>28790239</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>2717286.24767827</t>
+          <t>3937746.969530968</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>13349874.52351458</t>
+          <t>10650280.93972081</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>152480981.0</t>
+          <t>55697413.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5464.202</t>
+          <t>5342.422</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>26.31</v>
+        <v>26.44</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.44</v>
+        <v>26.46</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>431.15</t>
+          <t>233.09</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-98.40</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>45377257.2</v>
+        <v>70442197.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32709143.1</t>
+          <t>44592596.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>27633591.24</v>
+        <v>30181049.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>12668114</t>
+          <t>25849600</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>784088.3793443948</t>
+          <t>2717286.24767827</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6359987.553094462</t>
+          <t>13349874.52351458</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>153330525.0</t>
+          <t>152480981.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>351.187</t>
+          <t>5464.202</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,54 +7464,54 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>26.17</v>
+        <v>26.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2443.17</t>
+          <t>431.15</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-100.12</t>
+          <t>-98.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>17530372.6</v>
+        <v>45377257.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20604449.0</t>
+          <t>32709143.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>25677675.12</v>
+        <v>27633591.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3074076</t>
+          <t>12668114</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-229711.4704283447</t>
+          <t>784088.3793443948</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3943730.245830517</t>
+          <t>6359987.553094462</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>9363458.0</t>
+          <t>153330525.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>548.239</t>
+          <t>351.187</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-27.38</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
           <t>52.94</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>59.71</t>
-        </is>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>26.12</v>
+        <v>26.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>26.45</v>
+        <v>26.42</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>2443.17</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.12</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>19145978.8</v>
+        <v>17530372.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>26363928.6</t>
+          <t>20604449.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>27156087.18</v>
+        <v>25677675.12</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-7217949</t>
+          <t>-3074076</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>445564.6705538686</t>
+          <t>-229711.4704283447</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3097436.699800827</t>
+          <t>-3943730.245830517</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14581530.0</t>
+          <t>9363458.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>26.55</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>843.339</t>
+          <t>548.239</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-60.97</t>
+          <t>-27.38</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>59.71</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>26.1</v>
+        <v>26.12</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.48</v>
+        <v>26.45</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>212.78</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-101.69</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>19510303</v>
+        <v>19145978.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49984567.5</t>
+          <t>26363928.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>27612703.3</v>
+        <v>27156087.18</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-30474264</t>
+          <t>-7217949</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1089746.737891086</t>
+          <t>445564.6705538686</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2336902.323336951</t>
+          <t>-3097436.699800827</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>22454494.0</t>
+          <t>14581530.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1012.146</t>
+          <t>843.339</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-61.81</t>
+          <t>-60.97</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,63 +8754,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>58.73</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>26.06</v>
+        <v>26.1</v>
       </c>
       <c r="AN20" t="n">
-        <v>26.52</v>
+        <v>26.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>165.77</t>
+          <t>212.78</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-101.69</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>18742996</v>
+        <v>19510303</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>49081821.3</t>
+          <t>49984567.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>28629095.72</v>
+        <v>27612703.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-30338825</t>
+          <t>-30474264</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1712773.839932547</t>
+          <t>1089746.737891086</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-2010495.702555094</t>
+          <t>-2336902.323336951</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>27156279.0</t>
+          <t>22454494.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>26.45</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>27.25</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>26.45</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>26.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>537.759</t>
+          <t>1012.146</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-58.05</t>
+          <t>-61.81</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>56.11</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>26.38</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>26.02</v>
+        <v>26.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.57</v>
+        <v>26.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>165.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-103.66</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>20041029</v>
+        <v>18742996</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>47775762.3</t>
+          <t>49081821.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>35789543.06</v>
+        <v>28629095.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-27734733</t>
+          <t>-30338825</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>2389731.938566664</t>
+          <t>1712773.839932547</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1976159.790632617</t>
+          <t>-2010495.702555094</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14096102.0</t>
+          <t>27156279.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>669.773</t>
+          <t>537.759</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-50.45</t>
+          <t>-58.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.99</v>
+        <v>26.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>26.62</v>
+        <v>26.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.47</t>
+          <t>-103.66</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>23678525.4</v>
+        <v>20041029</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>47782500.4</t>
+          <t>47775762.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>37885324.3</v>
+        <v>35789543.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-24103975</t>
+          <t>-27734733</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3183530.434784716</t>
+          <t>2389731.938566664</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-457226.6739350557</t>
+          <t>-1976159.790632617</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>17441489.0</t>
+          <t>14096102.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>623.872</t>
+          <t>669.773</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-50.45</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>26.51</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.97</v>
+        <v>25.99</v>
       </c>
       <c r="AN23" t="n">
-        <v>26.64</v>
+        <v>26.62</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.36</t>
+          <t>-104.47</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>158312102.0470085</t>
+          <t>158305070.8271693</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>33581878.4</v>
+        <v>23678525.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>47528755.4</t>
+          <t>47782500.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>39069391.12</v>
+        <v>37885324.3</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-13946877</t>
+          <t>-24103975</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>3845486.272733765</t>
+          <t>3183530.434784716</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1370572.98113057</t>
+          <t>-457226.6739350557</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>16403151.0</t>
+          <t>17441489.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動售票機.xlsx
+++ b/Result/checksun_type/自動售票機.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>41.05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-43.00</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>32.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>41.91</v>
+        <v>41.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.04</v>
+        <v>43.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.82</t>
+          <t>-117.36</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7689.060085836909</t>
+          <t>7687.838571428571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6723.0</t>
+          <t>4556.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5839.4</v>
+        <v>5930.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4297.6</t>
+          <t>4343.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2636.96</v>
+        <v>2704.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>318.0348599446734</t>
+          <t>330.3639078684434</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>496.750557768979</t>
+          <t>398.173671449179</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6723.0</t>
+          <t>4556.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-43.70</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.10</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.17</v>
+        <v>44.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.16</t>
+          <t>-117.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7689.060085836909</t>
+          <t>7687.838571428571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>868.0</t>
+          <t>6723.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5212</v>
+        <v>5839.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4234.1</t>
+          <t>4297.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2509.54</v>
+        <v>2636.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>285.5410967038906</t>
+          <t>318.0348599446734</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>387.6550183055151</t>
+          <t>496.750557768979</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>868.0</t>
+          <t>6723.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>23.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-43.27</t>
+          <t>-43.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>42.19</v>
+        <v>42.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>44.31</v>
+        <v>44.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.34</t>
+          <t>-118.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7689.060085836909</t>
+          <t>7687.838571428571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5436</v>
+        <v>5212</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4501.8</t>
+          <t>4234.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2505.62</v>
+        <v>2509.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>977</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>266.9749291399588</t>
+          <t>285.5410967038906</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>845.2808541325121</t>
+          <t>387.6550183055151</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14149.0</t>
+          <t>868.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>-43.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>346.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-43.41</t>
+          <t>-43.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,63 +2309,63 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>42.36</v>
+        <v>42.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.45</v>
+        <v>44.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.29</t>
+          <t>-118.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7689.060085836909</t>
+          <t>7687.838571428571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3214.4</v>
+        <v>5436</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3897.5</t>
+          <t>4501.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2233.16</v>
+        <v>2505.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-683</t>
+          <t>934</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>161.8283973231309</t>
+          <t>266.9749291399588</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>45.8791605234901</t>
+          <t>845.2808541325121</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>14149.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-44.11</t>
+          <t>-43.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,27 +2739,27 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2769,38 +2769,38 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.73999999999999</t>
         </is>
       <